--- a/assignment3/data/trainingdataset_ontario_budgets_v6_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v6_llm_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F9E831-93DE-054E-A379-22BA59F3B604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AF1DE3-9D38-EB4B-9CF3-2E443094143E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8320" yWindow="980" windowWidth="26940" windowHeight="20100" activeTab="1" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
+    <workbookView xWindow="8320" yWindow="980" windowWidth="26940" windowHeight="20100" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4734,7 +4734,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
         <v>5</v>
@@ -18819,7 +18819,7 @@
     <row r="8" spans="1:4">
       <c r="A8">
         <f>COUNTIF(Sheet1!D:D,"0")</f>
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B8">
         <f>COUNTIF(Sheet1!D:D," ")</f>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="C8">
         <f>COUNTIF(Sheet1!D:D,"1")</f>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D8">
         <f>SUM(A8:C8)</f>
